--- a/Gravedigger2026/Assets/ConfigTables/Excel/推图战_刷怪配置表_PushMap_PushMapSpawnConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/推图战_刷怪配置表_PushMap_PushMapSpawnConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
   <si>
     <t>玩法配置ID</t>
   </si>
@@ -130,13 +130,13 @@
     <t>2</t>
   </si>
   <si>
+    <t>SP_03</t>
+  </si>
+  <si>
+    <t>TZ_01</t>
+  </si>
+  <si>
     <t>SP_02</t>
-  </si>
-  <si>
-    <t>TZ_01</t>
-  </si>
-  <si>
-    <t>SP_03</t>
   </si>
   <si>
     <t>Monster_03</t>
@@ -158,14 +158,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -627,148 +620,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1122,10 +1115,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="12.25" customWidth="1"/>
-    <col min="3" max="3" width="13.25" customWidth="1"/>
+    <col min="1" max="1" width="12.2545454545455" customWidth="1"/>
+    <col min="3" max="3" width="13.2545454545455" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1217,7 +1210,7 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
         <v>27</v>
@@ -1243,7 +1236,7 @@
         <v>30</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E5" t="s">
         <v>27</v>
@@ -1269,10 +1262,10 @@
         <v>26</v>
       </c>
       <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
+        <v>30</v>
+      </c>
+      <c r="E6">
+        <v>2</v>
       </c>
       <c r="F6" t="s">
         <v>33</v>
@@ -1295,10 +1288,10 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>10</v>
-      </c>
-      <c r="E7" t="s">
-        <v>31</v>
+        <v>30</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
       </c>
       <c r="F7" t="s">
         <v>28</v>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/推图战_刷怪配置表_PushMap_PushMapSpawnConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/推图战_刷怪配置表_PushMap_PushMapSpawnConfig.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\CursorGame_Git\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12280"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="38">
   <si>
     <t>玩法配置ID</t>
   </si>
@@ -124,7 +124,7 @@
     <t>0</t>
   </si>
   <si>
-    <t>Monster_02</t>
+    <t>Monster_04</t>
   </si>
   <si>
     <t>2</t>
@@ -142,10 +142,10 @@
     <t>Monster_03</t>
   </si>
   <si>
+    <t>Monster_11</t>
+  </si>
+  <si>
     <t>Boss_01</t>
-  </si>
-  <si>
-    <t>Monster_04</t>
   </si>
 </sst>
 </file>
@@ -1114,11 +1114,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="7" outlineLevelCol="7"/>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="12.2545454545455" customWidth="1"/>
-    <col min="3" max="3" width="13.2545454545455" customWidth="1"/>
+    <col min="1" max="1" width="12.2583333333333" customWidth="1"/>
+    <col min="3" max="3" width="13.2583333333333" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1288,7 +1288,7 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E7">
         <v>3</v>
@@ -1308,24 +1308,50 @@
         <v>24</v>
       </c>
       <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
         <v>36</v>
       </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>27</v>
-      </c>
-      <c r="E8" t="s">
-        <v>29</v>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>3</v>
       </c>
       <c r="F8" t="s">
         <v>28</v>
       </c>
       <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" t="s">
         <v>27</v>
       </c>
-      <c r="H8" t="s">
+      <c r="E9" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" t="s">
         <v>27</v>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/推图战_刷怪配置表_PushMap_PushMapSpawnConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/推图战_刷怪配置表_PushMap_PushMapSpawnConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,11 @@
           <t>同点出怪顺序</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>初始朝向</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -499,6 +504,11 @@
           <t>同 SpawnPointId 多行时升序</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0=每怪随机1~8；1正上/2右上/3正右/4右下/5正下/6左下/7正左/8左上；缺省5</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -541,6 +551,11 @@
           <t>SpawnOrder</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>InitialFacing</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -568,7 +583,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>0</t>
@@ -578,6 +592,9 @@
         <is>
           <t>1</t>
         </is>
+      </c>
+      <c r="I4" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="5">
@@ -606,7 +623,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>0</t>
@@ -616,6 +632,9 @@
         <is>
           <t>2</t>
         </is>
+      </c>
+      <c r="I5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -659,6 +678,9 @@
           <t>1</t>
         </is>
       </c>
+      <c r="I6" t="n">
+        <v>5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -686,7 +708,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>0</t>
@@ -696,6 +717,9 @@
         <is>
           <t>1</t>
         </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -724,7 +748,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>0</t>
@@ -734,6 +757,9 @@
         <is>
           <t>2</t>
         </is>
+      </c>
+      <c r="I8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -762,7 +788,6 @@
           <t>0</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
           <t>1</t>
@@ -772,6 +797,9 @@
         <is>
           <t>1</t>
         </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
